--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99F6665-558B-4087-8E07-B8D6823055A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="6" r:id="rId1"/>
-    <sheet name="Register" sheetId="7" r:id="rId2"/>
-    <sheet name="Product" sheetId="20" r:id="rId3"/>
-    <sheet name="Cart" sheetId="5" r:id="rId4"/>
-    <sheet name="Checkout" sheetId="3" r:id="rId5"/>
-    <sheet name="Filter" sheetId="8" r:id="rId6"/>
-    <sheet name="Order" sheetId="10" r:id="rId7"/>
-    <sheet name="IntegratedTests" sheetId="12" r:id="rId8"/>
+    <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
+    <sheet sheetId="7" name="Register" state="visible" r:id="rId5"/>
+    <sheet sheetId="20" name="Product" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Cart" state="visible" r:id="rId7"/>
+    <sheet sheetId="3" name="Checkout" state="visible" r:id="rId8"/>
+    <sheet sheetId="8" name="Filter" state="visible" r:id="rId9"/>
+    <sheet sheetId="10" name="Order" state="visible" r:id="rId10"/>
+    <sheet sheetId="12" name="IntegratedTests" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="223">
   <si>
     <t>ID</t>
   </si>
@@ -54,7 +53,7 @@
     <t>Đã có tài khoản</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -72,7 +71,7 @@
     <t>Đăng nhập với email sai</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
@@ -88,7 +87,7 @@
     <t>Đăng nhập với mật khẩu sai</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu không hợp lệ
@@ -104,7 +103,7 @@
     <t>Đăng nhập với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
@@ -120,7 +119,7 @@
     <t>Đăng nhập với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -136,7 +135,7 @@
     <t>Đăng nhập với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
@@ -152,7 +151,7 @@
     <t>Đăng nhập với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
@@ -168,7 +167,7 @@
     <t>Đăng nhập với thông tin đăng nhập của một tài khoản không có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -181,7 +180,7 @@
     <t>TC_LA_1</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập admin (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -195,7 +194,7 @@
     <t>TC_LA_2</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
@@ -208,7 +207,7 @@
     <t>TC_LA_3</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu không hợp lệ
@@ -218,7 +217,7 @@
     <t>TC_LA_4</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
@@ -231,7 +230,7 @@
     <t>TC_LA_5</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -241,7 +240,7 @@
     <t>TC_LA_6</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
@@ -254,7 +253,7 @@
     <t>TC_LA_7</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
@@ -270,7 +269,7 @@
     <t>Đăng ký vói thông tin hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng ký (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký
@@ -287,7 +286,7 @@
     <t>Đăng ký với mật khẩu không khớp</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu không khớp
@@ -303,7 +302,7 @@
     <t>Đăng ký với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email bỏ trống
@@ -316,7 +315,7 @@
     <t>Đăng ký với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu bỏ trống
@@ -332,7 +331,7 @@
     <t>Đăng ký với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email "nguyenquocthang909@gmail."
@@ -345,7 +344,7 @@
     <t>Đăng ký với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu "12345"
@@ -358,7 +357,7 @@
     <t>Đăng ký với thông tin đăng ký của một tài khoản đã có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký đã tồn tại
@@ -392,7 +391,7 @@
     <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận danh sách sản phẩm hiển thị thành công</t>
@@ -407,7 +406,7 @@
     <t>Xem chi tiết sản phẩm</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
@@ -423,7 +422,7 @@
     <t>Hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn kích cỡ và màu</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
@@ -441,7 +440,7 @@
     <t>Hiển thị thông tin sản phẩm khách hàng muốn mua sau khi chọn màu và kích cỡ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
@@ -459,11 +458,11 @@
     <t>Thông tin sản phẩm khách hàng muốn mua cập nhật sau khi đổi màu</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có kích cỡ và màu đa dạng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
@@ -478,7 +477,7 @@
     <t>Thông tin sản phẩm khách hàng muốn mua cập nhật sau khi đổi kích cỡ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm chọn ngẫu nhiên
@@ -496,11 +495,11 @@
     <t>Thêm vào giỏ hàng thành công</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có tồn kho lớn hơn 0</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Bấm nút đăng nhập
@@ -533,11 +532,11 @@
     <t>Sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -558,11 +557,11 @@
     <t>Tăng SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 0 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Xác nhận trang bán hoa hiển thị thành công
@@ -588,11 +587,11 @@
     <t>Giảm SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 1 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -617,7 +616,7 @@
     <t>Xoá sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -633,13 +632,28 @@
 14.	Xác nhận sản phẩm đước xoá từ giỏ hàng</t>
   </si>
   <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Phone No.</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>TC_CO_1</t>
   </si>
   <si>
     <t>Thanh toán thành công</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -660,6 +674,21 @@
 15.	Xác nhận trang thanh toán thông báo thành công</t>
   </si>
   <si>
+    <t>Nguyễn</t>
+  </si>
+  <si>
+    <t>Quốc Thắng</t>
+  </si>
+  <si>
+    <t>090754212</t>
+  </si>
+  <si>
+    <t>208 Sư Vạn Hạnh</t>
+  </si>
+  <si>
+    <t>Giao hàng cẩn thận</t>
+  </si>
+  <si>
     <t>Hiện thông báo "Create order success!" và dialog "Đặt hàng thành công"</t>
   </si>
   <si>
@@ -669,12 +698,12 @@
     <t>Thanh toán với voucher hết hạn</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng
 Có ít nhất 1 voucher</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -704,7 +733,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập họ để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -721,7 +750,7 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
-    <t>Hiện lỗi "Firstname không được để trống"</t>
+    <t>Firstname không được để trống</t>
   </si>
   <si>
     <t>TC_CO_4</t>
@@ -730,7 +759,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập tên để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -747,7 +776,7 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
-    <t>Hiện lỗi "Lastname không được để trống"</t>
+    <t>Lastname không được để trống</t>
   </si>
   <si>
     <t>TC_CO_5</t>
@@ -756,7 +785,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -773,7 +802,7 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
-    <t>Hiện lỗi "Email không được để trống"</t>
+    <t>Email không được để trống</t>
   </si>
   <si>
     <t>TC_CO_6</t>
@@ -782,7 +811,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>Hiện lỗi "Email không hợp lệ"</t>
+    <t>Email không hợp lệ</t>
   </si>
   <si>
     <t>TC_CO_7</t>
@@ -791,7 +820,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập SĐT để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -808,19 +837,22 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
-    <t>Hiện lỗi "Số điện thoại không hợp lệ"</t>
+    <t>Số điện thoại không hợp lệ</t>
   </si>
   <si>
     <t>TC_CO_8</t>
   </si>
   <si>
+    <t>Địa chỉ không được để trống</t>
+  </si>
+  <si>
     <t>TC_CO_9</t>
   </si>
   <si>
     <t>Thanh toán với thông tin thanh toán trường nhập ghi chú để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -837,7 +869,7 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
-    <t>Hiện thông báo "note is not allowed to be empty"</t>
+    <t>note is not allowed to be empty</t>
   </si>
   <si>
     <t>TC_F_1</t>
@@ -846,7 +878,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -864,7 +896,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -882,7 +914,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.     kéo thanh lọc giá đến giá trị định sẵn
@@ -907,7 +939,7 @@
     <t>Lọc sản phẩm theo loại hoa</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Bấm 1 trong 4 danh mục loại hoa
@@ -923,7 +955,7 @@
     <t>Lọc sản phẩm theo hãng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Bấm 1 trong 5 danh mục hãng hoa
@@ -939,7 +971,7 @@
     <t>Xem chi tiết đơn hàng được làm nổi bật</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -960,7 +992,7 @@
     <t>Xem chi tiết đơn hàng trong danh sách</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -978,7 +1010,7 @@
     <t>Huỷ đơn hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -1004,7 +1036,7 @@
     <t>Huỷ đơn hàng không có lý do</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -1038,40 +1070,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1087,7 +1119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1184,11 +1216,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1214,10 +1266,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1231,30 +1325,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1588,29 +1658,29 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="39.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="47.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -1619,239 +1689,79 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
+    <row r="2" ht="157.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>205</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" ht="156.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>209</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" ht="242.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" ht="228" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>216</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>22</v>
+        <v>217</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1859,154 +1769,71 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="7" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="7" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="7" customWidth="1"/>
-    <col min="5" max="6" width="29.75" style="7" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="25" customWidth="1"/>
+    <col min="3" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="114.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>83</v>
+    <row r="2" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.75" style="7" customWidth="1"/>
     <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
@@ -2017,49 +1844,49 @@
     <col min="10" max="10" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="19" t="s">
+      <c r="F1" s="12"/>
+      <c r="G1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="20"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" s="14"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" ht="72" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>89</v>
       </c>
@@ -2078,7 +1905,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="128.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>94</v>
       </c>
@@ -2097,7 +1924,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="142.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>98</v>
       </c>
@@ -2116,7 +1943,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="142.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>102</v>
       </c>
@@ -2135,7 +1962,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="142.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>106</v>
       </c>
@@ -2154,7 +1981,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="142.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="142.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>110</v>
       </c>
@@ -2173,7 +2000,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C9" s="1"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -2182,24 +2009,508 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="39" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="3" customWidth="1"/>
+    <col min="12" max="13" width="24.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="6.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
@@ -2212,49 +2523,49 @@
     <col min="10" max="10" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="19" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" ht="285.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>114</v>
       </c>
@@ -2267,10 +2578,10 @@
       <c r="D3" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="18" t="s">
         <v>119</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -2283,7 +2594,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>121</v>
       </c>
@@ -2296,10 +2607,10 @@
       <c r="D4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="18" t="s">
         <v>119</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2312,7 +2623,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -2325,10 +2636,10 @@
       <c r="D5" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="18" t="s">
         <v>119</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2341,7 +2652,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>130</v>
       </c>
@@ -2354,10 +2665,10 @@
       <c r="D6" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="18" t="s">
         <v>119</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -2370,7 +2681,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="256.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>135</v>
       </c>
@@ -2383,10 +2694,10 @@
       <c r="D7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="18" t="s">
         <v>119</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -2399,43 +2710,43 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="185.25" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C8" s="8"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="39.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="39.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="35.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2448,7 +2759,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -2458,312 +2769,232 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="357" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="100.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>140</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>157</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="71.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="114" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7.5" style="11" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="22.75" style="11" customWidth="1"/>
-    <col min="4" max="4" width="36.875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="11" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="171" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>192</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2772,28 +3003,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="47.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.75" style="7" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="7" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="7" customWidth="1"/>
+    <col min="5" max="6" width="29.75" style="7" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="7" customWidth="1"/>
     <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -2802,140 +3032,268 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>193</v>
+    <row r="2" ht="114.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>195</v>
+        <v>60</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="228" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="85.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="11" customWidth="1"/>
-    <col min="3" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="25" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="22.75" style="25" customWidth="1"/>
+    <col min="4" max="4" width="36.875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="25" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="25" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="11" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11" t="s">
-        <v>211</v>
+    <row r="2" ht="157.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="171" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" ht="185.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" ht="185.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" ht="99.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="221">
   <si>
     <t>ID</t>
   </si>
@@ -683,13 +683,16 @@
     <t>090754212</t>
   </si>
   <si>
-    <t>208 Sư Vạn Hạnh</t>
+    <t>FAIL</t>
   </si>
   <si>
     <t>Giao hàng cẩn thận</t>
   </si>
   <si>
     <t>Hiện thông báo "Create order success!" và dialog "Đặt hàng thành công"</t>
+  </si>
+  <si>
+    <t>TypeError: Invalid locator</t>
   </si>
   <si>
     <t>TC_CO_2</t>
@@ -724,6 +727,9 @@
 15.	Xác nhận trang thanh toán thông báo lỗi</t>
   </si>
   <si>
+    <t>208 Sư Vạn Hạnh</t>
+  </si>
+  <si>
     <t>Hiện thông báo "Đặt hàng thất bại!"</t>
   </si>
   <si>
@@ -872,6 +878,9 @@
     <t>note is not allowed to be empty</t>
   </si>
   <si>
+    <t>Keyword</t>
+  </si>
+  <si>
     <t>TC_F_1</t>
   </si>
   <si>
@@ -884,10 +893,13 @@
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
 5.	Bấm nút thanh tìm kiếm
 6.	Nhập từ khoá “Gucci” và bấm Enter hoặc icon kính lúp
-7.	Xác nhận danh sách sản phẩm hiển thị bao gồm từ khoá đó</t>
-  </si>
-  <si>
-    <t>Danh sách sản phẩm hiển thị bao gồm từ khoá đó</t>
+7.	Xác nhận danh sách sản phẩm có áp dụng lọc</t>
+  </si>
+  <si>
+    <t>Gucci</t>
+  </si>
+  <si>
+    <t>Danh sách sản phẩm hiển thị bao gồm từ khoá</t>
   </si>
   <si>
     <t>TC_F_2</t>
@@ -905,64 +917,45 @@
 7.	Xác nhận danh sách sản phẩm hiển thị “Không tìm thấy sản phẩm nào phù hợp với "fake"</t>
   </si>
   <si>
-    <t>Danh sách sản phẩm hiển thị “Không tìm thấy sản phẩm nào phù hợp với "fake"</t>
+    <t>fake</t>
+  </si>
+  <si>
+    <t>Không tìm thấy sản phẩm nào phù hợp với "fake"</t>
   </si>
   <si>
     <t>TC_F_3</t>
   </si>
   <si>
-    <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá không tồn tại trong các sản phẩm</t>
+    <t>Tìm kiếm và lọc sản phẩm theo giá</t>
   </si>
   <si>
     <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
-4.     kéo thanh lọc giá đến giá trị định sẵn
+4.	Kéo thanh lọc giá đến giá trị định sẵn
 5.	Xác nhận thanh tìm kiếm hiển thị thành công
 6.	Bấm nút thanh tìm kiếm
 7.	Nhập từ khoá “fake” và bấm Enter hoặc icon kính lúp
-8.	Xác nhận danh sách sản phẩm hiển thị “Không tìm thấy sản phẩm nào phù hợp với "fake"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danh sách sản phẩm hiển thị bao gốm từ khóa giá đó </t>
+8.	Xác nhận danh sách sản phẩm có áp dụng lọc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danh sách sản phẩm hiển thị trong khoảng giá được đặt </t>
   </si>
   <si>
     <t>TC_F_4</t>
   </si>
   <si>
-    <t>Tìm kiếm và loc sản phẩm theo giá với từ khoá không tồn tại trong các sản phẩm</t>
-  </si>
-  <si>
-    <t>TC_F_5</t>
-  </si>
-  <si>
-    <t>Lọc sản phẩm theo loại hoa</t>
+    <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá</t>
   </si>
   <si>
     <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
-4.	Bấm 1 trong 4 danh mục loại hoa
-5.	Xác nhận danh sách sản phẩm hiển thị những sản phẩm từ loại hoa đó nếu có</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Danh sách sản phẩm hiển thị những sản phẩm từ loại hoa đó nếu có</t>
-  </si>
-  <si>
-    <t>TC_F_6</t>
-  </si>
-  <si>
-    <t>Lọc sản phẩm theo hãng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang bán hoa (localhost:4200)
-3.	Xác nhận trang bán hoa hiển thị thành công
-4.	Bấm 1 trong 5 danh mục hãng hoa
-5.	Xác nhận danh sách sản phẩm hiển thị những sản phẩm từ hãng đó nếu có</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Danh sách sản phẩm hiển thị những sản phẩm từ hãng đó nếu có</t>
+4.	Kéo thanh lọc giá đến giá trị định sẵn
+5.	Xác nhận thanh tìm kiếm hiển thị thành công
+6.	Bấm nút thanh tìm kiếm
+7.	Nhập từ khoá “Gucci” và bấm Enter hoặc icon kính lúp
+8.	Xác nhận danh sách sản phẩm có áp dụng lọc</t>
   </si>
   <si>
     <t>TC_TXN_1</t>
@@ -1100,8 +1093,8 @@
       <name val="Arial"/>
     </font>
     <font>
-      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
@@ -1314,14 +1307,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1665,15 +1658,14 @@
   <cols>
     <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="47.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1696,73 +1688,81 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="157.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" ht="243" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="256.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="3" ht="156.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" ht="384.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" ht="242.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="5" ht="228" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1775,7 +1775,7 @@
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="27" customWidth="1"/>
     <col min="3" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1783,13 +1783,13 @@
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="28" t="s">
@@ -1806,23 +1806,23 @@
       <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
+    <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="27" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2147,21 +2147,21 @@
         <v>151</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>118</v>
@@ -2179,16 +2179,16 @@
         <v>148</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>120</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>118</v>
@@ -2221,16 +2221,16 @@
         <v>148</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>120</v>
@@ -2238,16 +2238,16 @@
     </row>
     <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>118</v>
@@ -2263,16 +2263,16 @@
         <v>148</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K6" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>120</v>
@@ -2280,16 +2280,16 @@
     </row>
     <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>118</v>
@@ -2307,16 +2307,16 @@
         <v>148</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K7" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>120</v>
@@ -2324,16 +2324,16 @@
     </row>
     <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>118</v>
@@ -2351,16 +2351,16 @@
         <v>148</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K8" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>120</v>
@@ -2368,16 +2368,16 @@
     </row>
     <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>118</v>
@@ -2393,16 +2393,16 @@
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K9" s="18" t="s">
         <v>150</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>120</v>
@@ -2410,16 +2410,16 @@
     </row>
     <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>118</v>
@@ -2441,10 +2441,10 @@
         <v>150</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>120</v>
@@ -2452,16 +2452,16 @@
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>118</v>
@@ -2479,14 +2479,14 @@
         <v>148</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>120</v>
@@ -3148,85 +3148,102 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="25" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="25" customWidth="1"/>
-    <col min="3" max="3" width="22.75" style="25" customWidth="1"/>
-    <col min="4" max="4" width="36.875" style="25" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="25" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="25" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="25" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
+    <col min="2" max="3" width="36.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="45.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="33.125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="21"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="I1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="J1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="157.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="6" t="s">
+    <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="171" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" ht="185.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3235,68 +3252,88 @@
       <c r="D4" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="185.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" ht="128.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="27" t="s">
         <v>195</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>119</v>
+      </c>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="99.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" ht="128.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" ht="99.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>203</v>
-      </c>
+      <c r="I6" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="221">
   <si>
     <t>ID</t>
   </si>
@@ -3271,7 +3271,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" ht="128.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>195</v>
       </c>
@@ -3294,9 +3294,14 @@
       <c r="H5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="128.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>199</v>
       </c>
@@ -3321,7 +3326,12 @@
       <c r="H6" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J6" t="s">
+        <v>120</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD6C71F-5756-4C8F-A740-E3A4C31D2011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="6" r:id="rId1"/>
-    <sheet name="Register" sheetId="7" r:id="rId2"/>
-    <sheet name="Cart" sheetId="5" r:id="rId3"/>
-    <sheet name="Checkout" sheetId="3" r:id="rId4"/>
-    <sheet name="Filter" sheetId="8" r:id="rId5"/>
-    <sheet name="Order" sheetId="10" r:id="rId6"/>
-    <sheet name="IntegratedTests" sheetId="12" r:id="rId7"/>
+    <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
+    <sheet sheetId="7" name="Register" state="visible" r:id="rId5"/>
+    <sheet sheetId="5" name="Cart" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Checkout" state="visible" r:id="rId7"/>
+    <sheet sheetId="8" name="Filter" state="visible" r:id="rId8"/>
+    <sheet sheetId="10" name="Order" state="visible" r:id="rId9"/>
+    <sheet sheetId="12" name="IntegratedTests" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="166">
   <si>
     <t>ID</t>
   </si>
@@ -62,7 +61,7 @@
     <t>Đã có tài khoản</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -80,52 +79,42 @@
     <t>Người dùng đăng nhập thành công và được chuyển đến trang chủ</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>TC_LC_2</t>
   </si>
   <si>
     <t>Đăng nhập với email sai</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
+    <t>nguyenquocthang9@gmail.com</t>
+  </si>
+  <si>
     <t>Email not found!</t>
   </si>
   <si>
-    <t>TC_LC_3</t>
-  </si>
-  <si>
-    <t>Đăng nhập với mật khẩu sai</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:4200/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với mật khẩu không hợp lệ
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Password not match!</t>
-  </si>
-  <si>
     <t>TC_LC_4</t>
   </si>
   <si>
     <t>Đăng nhập với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
-    <t>"Email không được để trống</t>
+    <t>Email không được để trống</t>
   </si>
   <si>
     <t>TC_LC_5</t>
@@ -134,7 +123,7 @@
     <t>Đăng nhập với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -150,13 +139,16 @@
     <t>Đăng nhập với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
+    <t>nguyenquocthang909</t>
+  </si>
+  <si>
     <t>Email không hợp lệ</t>
   </si>
   <si>
@@ -166,116 +158,17 @@
     <t>Đăng nhập với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
-    <t xml:space="preserve"> "Mật khẩu phải có ít nhất 6 ký tự"</t>
-  </si>
-  <si>
-    <t>TC_LC_8</t>
-  </si>
-  <si>
-    <t>Đăng nhập với thông tin đăng nhập của một tài khoản không có tồn tại trong CSDL</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:4200/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Hiển thị thông báo "Tài khoản không tồn tại"</t>
-  </si>
-  <si>
-    <t>TC_LA_1</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập admin (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập
-5.	Bấm nút đăng nhập
-6.	Xác nhận trang admin dashboard hiển thị thành công</t>
-  </si>
-  <si>
-    <t>Hiển thị thông báo "Đăng nhập thành công!" và chuyển qua trang dashboard</t>
-  </si>
-  <si>
-    <t>TC_LA_2</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với email không hợp lệ
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Tài khoản hoặc mật khẩu không đúng</t>
-  </si>
-  <si>
-    <t>TC_LA_3</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với mật khẩu không hợp lệ
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>TC_LA_4</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với email bỏ trống
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Trường này là bắt buộc</t>
-  </si>
-  <si>
-    <t>TC_LA_5</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>TC_LA_6</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Địa chỉ email không hợp lệ</t>
-  </si>
-  <si>
-    <t>TC_LA_7</t>
-  </si>
-  <si>
-    <t>1.	Mở trình duyệt tùy chọn
-2.	Truy cập trang đăng nhập (localhost:3000/auth/login)
-3.	Xác nhận trang đăng nhập hiển thị thành công
-4.	Nhập thông tin đăng nhập với mật khẩu "12345"
-5.	Xác nhận trang báo lỗi</t>
-  </si>
-  <si>
-    <t>Phải có ít nhất 6 ký tự</t>
+    <t>Aa</t>
+  </si>
+  <si>
+    <t>Mật khẩu phải có ít nhất 6 ký tự</t>
   </si>
   <si>
     <t>TC_R_1</t>
@@ -284,7 +177,7 @@
     <t>Đăng ký vói thông tin hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng ký (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký
@@ -301,7 +194,7 @@
     <t>Đăng ký với mật khẩu không khớp</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu không khớp
@@ -317,23 +210,20 @@
     <t>Đăng ký với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email bỏ trống
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
-    <t>Email không được để trống</t>
-  </si>
-  <si>
     <t>TC_R_4</t>
   </si>
   <si>
     <t>Đăng ký với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu bỏ trống
@@ -346,7 +236,7 @@
     <t>Đăng ký với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email "nguyenquocthang909@gmail."
@@ -359,23 +249,20 @@
     <t>Đăng ký với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu "12345"
 5.	Xác nhận trang báo lỗi</t>
   </si>
   <si>
-    <t>Mật khẩu phải có ít nhất 6 ký tự</t>
-  </si>
-  <si>
     <t>TC_R_7</t>
   </si>
   <si>
     <t>Đăng ký với thông tin đăng ký của một tài khoản đã có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký đã tồn tại
@@ -394,11 +281,11 @@
     <t>Thêm vào giỏ hàng thành công</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có tồn kho lớn hơn 0</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Bấm nút đăng nhập
@@ -416,20 +303,17 @@
 16.	Xác nhận icon giỏ hàng hiện nút số lượng sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>TC_AC_2</t>
   </si>
   <si>
     <t>Sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -450,11 +334,11 @@
     <t>Tăng SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 0 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Xác nhận trang bán hoa hiển thị thành công
@@ -480,11 +364,11 @@
     <t>Giảm SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 1 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -509,7 +393,7 @@
     <t>Xoá sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -546,7 +430,7 @@
     <t>Thanh toán thành công</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -594,12 +478,12 @@
     <t>Thanh toán với voucher hết hạn</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng
 Có ít nhất 1 voucher</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -632,7 +516,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập họ để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -658,7 +542,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập tên để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -684,7 +568,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -713,7 +597,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập SĐT để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -745,7 +629,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập ghi chú để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -777,7 +661,7 @@
     <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -798,7 +682,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -819,7 +703,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -838,7 +722,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -854,7 +738,7 @@
     <t>Xem chi tiết đơn hàng được làm nổi bật</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -875,7 +759,7 @@
     <t>Huỷ đơn hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -901,7 +785,7 @@
     <t>Huỷ đơn hàng không có lý do</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -935,40 +819,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -984,7 +868,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1002,35 +886,6 @@
       <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
@@ -1099,11 +954,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1135,6 +999,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1155,45 +1046,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1527,855 +1379,225 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="39.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="23" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="22"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="19"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" ht="243" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>151</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
+    </row>
+    <row r="4" ht="384.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>155</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>157</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>159</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="24" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
-    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="25" customWidth="1"/>
+    <col min="3" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+    <row r="1" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="25" t="s">
+      <c r="E1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="G1" s="26" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="10" t="s">
+    <row r="2" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="B2" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>165</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" style="2" customWidth="1"/>
-    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-    </row>
-    <row r="3" spans="1:9" ht="285.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="256.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="10"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
@@ -2393,43 +1615,43 @@
     <col min="15" max="15" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="25" t="s">
+      <c r="E1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="22"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
@@ -2437,36 +1659,36 @@
         <v>9</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="18"/>
-    </row>
-    <row r="3" spans="1:14" ht="357" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -2475,42 +1697,42 @@
         <v>15</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -2519,42 +1741,42 @@
         <v>15</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -2564,39 +1786,39 @@
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>14</v>
@@ -2605,128 +1827,128 @@
         <v>15</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="C9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>14</v>
@@ -2735,40 +1957,40 @@
         <v>15</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="B10" s="2" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
@@ -2777,40 +1999,40 @@
         <v>15</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>14</v>
@@ -2819,47 +2041,746 @@
         <v>15</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="2" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17" style="2" customWidth="1"/>
+    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="13"/>
+      <c r="G1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="185.25" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="10"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="44.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="100.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="114" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" ht="85.5" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" ht="99.75" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="9" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
+    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="36.625" style="2" customWidth="1"/>
@@ -2871,64 +2792,64 @@
     <col min="10" max="10" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28" t="s">
+      <c r="F1" s="17"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="12" t="s">
+    <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:10" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -2937,30 +2858,30 @@
         <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -2969,30 +2890,30 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="J4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>170</v>
+        <v>143</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -3001,27 +2922,27 @@
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>148</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -3030,244 +2951,29 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-    </row>
-    <row r="3" spans="1:9" ht="243" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="384.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="16" customWidth="1"/>
-    <col min="3" max="8" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="16" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="16" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="16" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="167">
   <si>
     <t>ID</t>
   </si>
@@ -185,7 +185,10 @@
 6.	Xác nhận trang bán hoa hiển thị thành công sau khi đăng ký</t>
   </si>
   <si>
-    <t>Chuyển qua trang bán hoa hiển thị sau khi đăng ký thành công</t>
+    <t>validemail1@gmail.com</t>
+  </si>
+  <si>
+    <t>Chuyển qua trang đăng nhập hiển thị sau khi đăng ký thành công</t>
   </si>
   <si>
     <t>TC_R_2</t>
@@ -820,7 +823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -845,6 +848,10 @@
     </font>
     <font>
       <family val="2"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
@@ -967,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -998,6 +1005,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1032,7 +1045,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1396,7 +1409,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1423,7 +1436,7 @@
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
+      <c r="A2" s="21"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1439,28 +1452,28 @@
     </row>
     <row r="3" ht="243" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -1468,28 +1481,28 @@
     </row>
     <row r="4" ht="384.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>17</v>
@@ -1497,25 +1510,25 @@
     </row>
     <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1539,54 +1552,54 @@
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="27" customWidth="1"/>
     <col min="3" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>162</v>
+        <v>67</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>163</v>
+      <c r="B3" s="27" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>164</v>
+      <c r="B4" s="27" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>165</v>
+      <c r="B5" s="27" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1616,27 +1629,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="13"/>
+      <c r="E1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
@@ -1648,10 +1661,10 @@
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1659,19 +1672,19 @@
         <v>9</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -1679,16 +1692,16 @@
     </row>
     <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -1697,42 +1710,42 @@
         <v>15</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -1741,25 +1754,25 @@
         <v>15</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>17</v>
@@ -1767,16 +1780,16 @@
     </row>
     <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -1786,22 +1799,22 @@
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>17</v>
@@ -1809,16 +1822,16 @@
     </row>
     <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>14</v>
@@ -1827,23 +1840,23 @@
         <v>15</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
@@ -1851,37 +1864,37 @@
     </row>
     <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>26</v>
@@ -1895,37 +1908,37 @@
     </row>
     <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>35</v>
@@ -1939,16 +1952,16 @@
     </row>
     <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>14</v>
@@ -1957,23 +1970,23 @@
         <v>15</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>17</v>
@@ -1981,16 +1994,16 @@
     </row>
     <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
@@ -1999,23 +2012,23 @@
         <v>15</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>17</v>
@@ -2023,16 +2036,16 @@
     </row>
     <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>14</v>
@@ -2041,23 +2054,23 @@
         <v>15</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>17</v>
@@ -2095,59 +2108,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="11" t="s">
+      <c r="E1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -2156,10 +2169,10 @@
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -2167,16 +2180,16 @@
     </row>
     <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -2185,10 +2198,10 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>17</v>
@@ -2196,16 +2209,16 @@
     </row>
     <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -2214,10 +2227,10 @@
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>17</v>
@@ -2225,16 +2238,16 @@
     </row>
     <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -2243,10 +2256,10 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>17</v>
@@ -2254,16 +2267,16 @@
     </row>
     <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>14</v>
@@ -2272,10 +2285,10 @@
         <v>15</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>17</v>
@@ -2586,7 +2599,7 @@
     <col min="3" max="3" width="14" style="9" customWidth="1"/>
     <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
     <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="25.375" style="9" customWidth="1"/>
     <col min="8" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2639,47 +2652,64 @@
       <c r="B3" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="E3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C4" s="9"/>
       <c r="D4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
     <row r="5" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C5" s="9"/>
       <c r="D5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
@@ -2688,16 +2718,19 @@
     </row>
     <row r="6" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C6" s="9"/>
       <c r="D6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="12"/>
       <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
@@ -2706,16 +2739,21 @@
     </row>
     <row r="7" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C7" s="9"/>
       <c r="D7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2724,16 +2762,21 @@
     </row>
     <row r="8" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C8" s="9"/>
       <c r="D8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="G8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2742,21 +2785,25 @@
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -2793,63 +2840,63 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="11" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="21" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="G2" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -2858,13 +2905,13 @@
         <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -2872,16 +2919,16 @@
     </row>
     <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -2890,13 +2937,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -2904,16 +2951,16 @@
     </row>
     <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="22" t="s">
         <v>144</v>
       </c>
+      <c r="B5" s="24" t="s">
+        <v>145</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -2922,10 +2969,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -2933,16 +2980,16 @@
     </row>
     <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="22" t="s">
         <v>148</v>
       </c>
+      <c r="B6" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -2951,13 +2998,13 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>

--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00E671D-820B-4CFB-858C-0A95B39A69A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
-    <sheet sheetId="7" name="Register" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="Cart" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="Checkout" state="visible" r:id="rId7"/>
-    <sheet sheetId="8" name="Filter" state="visible" r:id="rId8"/>
-    <sheet sheetId="10" name="Order" state="visible" r:id="rId9"/>
-    <sheet sheetId="12" name="IntegratedTests" state="visible" r:id="rId10"/>
+    <sheet name="Login" sheetId="6" r:id="rId1"/>
+    <sheet name="Register" sheetId="7" r:id="rId2"/>
+    <sheet name="Cart" sheetId="5" r:id="rId3"/>
+    <sheet name="Checkout" sheetId="3" r:id="rId4"/>
+    <sheet name="Filter" sheetId="8" r:id="rId5"/>
+    <sheet name="Order" sheetId="10" r:id="rId6"/>
+    <sheet name="IntegratedTests" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="167">
   <si>
     <t>ID</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Đã có tài khoản</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -88,7 +89,7 @@
     <t>Đăng nhập với email sai</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
@@ -107,7 +108,7 @@
     <t>Đăng nhập với email bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
@@ -123,7 +124,7 @@
     <t>Đăng nhập với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -139,7 +140,7 @@
     <t>Đăng nhập với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
@@ -158,7 +159,7 @@
     <t>Đăng nhập với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
@@ -177,7 +178,7 @@
     <t>Đăng ký vói thông tin hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng ký (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký
@@ -197,7 +198,7 @@
     <t>Đăng ký với mật khẩu không khớp</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu không khớp
@@ -213,7 +214,7 @@
     <t>Đăng ký với email bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email bỏ trống
@@ -226,7 +227,7 @@
     <t>Đăng ký với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu bỏ trống
@@ -239,7 +240,7 @@
     <t>Đăng ký với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email "nguyenquocthang909@gmail."
@@ -252,7 +253,7 @@
     <t>Đăng ký với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu "12345"
@@ -265,7 +266,7 @@
     <t>Đăng ký với thông tin đăng ký của một tài khoản đã có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký đã tồn tại
@@ -284,11 +285,11 @@
     <t>Thêm vào giỏ hàng thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có tồn kho lớn hơn 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Bấm nút đăng nhập
@@ -312,11 +313,11 @@
     <t>Sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -337,11 +338,11 @@
     <t>Tăng SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 0 trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Xác nhận trang bán hoa hiển thị thành công
@@ -367,11 +368,11 @@
     <t>Giảm SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 1 trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -396,7 +397,7 @@
     <t>Xoá sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -433,7 +434,7 @@
     <t>Thanh toán thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -481,12 +482,12 @@
     <t>Thanh toán với voucher hết hạn</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng
 Có ít nhất 1 voucher</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -519,7 +520,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập họ để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -545,7 +546,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập tên để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -571,7 +572,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -600,7 +601,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập SĐT để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -632,7 +633,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập ghi chú để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -664,7 +665,7 @@
     <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -685,7 +686,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -706,7 +707,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -725,7 +726,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -741,7 +742,7 @@
     <t>Xem chi tiết đơn hàng được làm nổi bật</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -762,7 +763,7 @@
     <t>Huỷ đơn hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -788,7 +789,7 @@
     <t>Huỷ đơn hàng không có lý do</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -822,44 +823,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -974,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1006,38 +1007,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1059,6 +1030,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1392,225 +1399,760 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" ht="243" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>151</v>
+      <c r="G2" s="20"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="384.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="25" t="s">
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="F8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="27" customWidth="1"/>
-    <col min="3" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="9" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
+    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
+    <col min="7" max="7" width="24.875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17" style="2" customWidth="1"/>
+    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:9" ht="285.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>166</v>
-      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="256.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="10"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
@@ -1628,43 +2170,43 @@
     <col min="15" max="15" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="5" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
+    <row r="2" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="27"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1686,11 +2228,11 @@
       <c r="K2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" ht="357" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -1734,7 +2276,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -1778,7 +2320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -1820,7 +2362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
@@ -1862,7 +2404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>117</v>
       </c>
@@ -1875,7 +2417,7 @@
       <c r="D7" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -1906,7 +2448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>120</v>
       </c>
@@ -1919,7 +2461,7 @@
       <c r="D8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1950,7 +2492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
@@ -1992,7 +2534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>126</v>
       </c>
@@ -2034,7 +2576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>128</v>
       </c>
@@ -2078,756 +2620,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" style="2" customWidth="1"/>
-    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-    </row>
-    <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="185.25" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="44.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="100.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" ht="114" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" ht="85.5" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" ht="99.75" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
-    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="25.375" style="9" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="36.625" style="2" customWidth="1"/>
@@ -2839,53 +2648,53 @@
     <col min="10" max="10" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="13" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="23" t="s">
+    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>133</v>
       </c>
@@ -2917,7 +2726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>139</v>
       </c>
@@ -2949,11 +2758,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="14" t="s">
         <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2978,11 +2787,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="14" t="s">
         <v>149</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3012,15 +2821,230 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="243" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="384.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="17" customWidth="1"/>
+    <col min="3" max="8" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00E671D-820B-4CFB-858C-0A95B39A69A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="6" r:id="rId1"/>
-    <sheet name="Register" sheetId="7" r:id="rId2"/>
-    <sheet name="Cart" sheetId="5" r:id="rId3"/>
-    <sheet name="Checkout" sheetId="3" r:id="rId4"/>
-    <sheet name="Filter" sheetId="8" r:id="rId5"/>
-    <sheet name="Order" sheetId="10" r:id="rId6"/>
-    <sheet name="IntegratedTests" sheetId="12" r:id="rId7"/>
+    <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
+    <sheet sheetId="7" name="Register" state="visible" r:id="rId5"/>
+    <sheet sheetId="5" name="Cart" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Checkout" state="visible" r:id="rId7"/>
+    <sheet sheetId="8" name="Filter" state="visible" r:id="rId8"/>
+    <sheet sheetId="10" name="Order" state="visible" r:id="rId9"/>
+    <sheet sheetId="12" name="IntegratedTests" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="180">
   <si>
     <t>ID</t>
   </si>
@@ -62,7 +61,7 @@
     <t>Đã có tài khoản</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -89,7 +88,7 @@
     <t>Đăng nhập với email sai</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
@@ -108,7 +107,7 @@
     <t>Đăng nhập với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
@@ -124,7 +123,7 @@
     <t>Đăng nhập với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -140,7 +139,7 @@
     <t>Đăng nhập với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
@@ -159,7 +158,7 @@
     <t>Đăng nhập với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
@@ -178,7 +177,7 @@
     <t>Đăng ký vói thông tin hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng ký (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký
@@ -198,7 +197,7 @@
     <t>Đăng ký với mật khẩu không khớp</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu không khớp
@@ -214,7 +213,7 @@
     <t>Đăng ký với email bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email bỏ trống
@@ -227,7 +226,7 @@
     <t>Đăng ký với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu bỏ trống
@@ -240,7 +239,7 @@
     <t>Đăng ký với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email "nguyenquocthang909@gmail."
@@ -253,7 +252,7 @@
     <t>Đăng ký với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu "12345"
@@ -266,7 +265,7 @@
     <t>Đăng ký với thông tin đăng ký của một tài khoản đã có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký đã tồn tại
@@ -285,11 +284,11 @@
     <t>Thêm vào giỏ hàng thành công</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có tồn kho lớn hơn 0</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Bấm nút đăng nhập
@@ -313,11 +312,11 @@
     <t>Sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -338,11 +337,11 @@
     <t>Tăng SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 0 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Xác nhận trang bán hoa hiển thị thành công
@@ -368,11 +367,11 @@
     <t>Giảm SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 1 trong giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -397,7 +396,7 @@
     <t>Xoá sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -434,7 +433,7 @@
     <t>Thanh toán thành công</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -482,12 +481,12 @@
     <t>Thanh toán với voucher hết hạn</t>
   </si>
   <si>
-    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng
 Có ít nhất 1 voucher</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -520,7 +519,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập họ để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -546,7 +545,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập tên để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -572,7 +571,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -601,7 +600,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập SĐT để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -633,7 +632,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập ghi chú để trống</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -665,7 +664,7 @@
     <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -686,7 +685,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -707,7 +706,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -726,7 +725,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -742,7 +741,7 @@
     <t>Xem chi tiết đơn hàng được làm nổi bật</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -763,7 +762,7 @@
     <t>Huỷ đơn hàng</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -789,7 +788,7 @@
     <t>Huỷ đơn hàng không có lý do</t>
   </si>
   <si>
-    <t>1.	Mở trình duyệt tùy chọn
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -808,59 +807,151 @@
     <t>Hiện thông báo "Vui lòng nhập lý do hủy đơn hàng!"</t>
   </si>
   <si>
-    <t>quản lý sản phẩm bên admin, kiểm sản phẩm bên client</t>
-  </si>
-  <si>
-    <t>quản lý khuyến mãi, kiểm khuyến mãi bên client</t>
-  </si>
-  <si>
-    <t>quản lý hãng/danh mục, kiểm hãng/danh mục bên client</t>
-  </si>
-  <si>
-    <t>quản lý đơn hàng, kiểm đơn hàng bên client</t>
+    <t>Quản lý đơn hàng bên admin và client</t>
+  </si>
+  <si>
+    <t>Phải có ít nhất 1 sản phẩm đang bán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng nhập (localhost:4200/login)
+3.	Xác nhận trang đăng nhập hiển thị thành công
+4.	Nhập thông tin đăng nhập
+5.	Xác nhận trang không báo lỗi
+6.	Bấm nút đăng nhập
+7.	Xác nhận trang bán hoa hiển thị thành công
+8.	Chọn sản phẩm bất kì
+9.	Chọn kích cỡ sản phẩm
+10.	Chọn màu sắc sản phẩm 
+11.	Nhấn nút "Thêm vào sản phẩm"
+12.	Nhấn vào icon giỏ hàng 
+13.	Xác nhận trang giỏ hàng hiển thị thành công 
+14.	Nhấn vào ô trống chọn sản phẩm cần thanh toán 
+15.	Nhấn nút "Tiến hành thanh toán"
+16.	Điền thông tin giao hàng 
+17.	Chọn phương thức thanh toán 
+18.	Chọn mã giảm giá
+19.	Nhấn nút "Thanh toán"
+20.	Truy cập trang admin (http://localhost:3000/)
+21.	Chọn mục "Các đơn hàng"
+22.	Xác nhận bảng đơn hàng có đơn hàng cần xử lý</t>
+  </si>
+  <si>
+    <t>Danh mục "Các đơn hàng" có đơn hàng cần xử lý</t>
+  </si>
+  <si>
+    <t>AssertionError [ERR_ASSERTION]: 0 != 0</t>
+  </si>
+  <si>
+    <t>Kiểm tra số lượng voucher bên admin sau khi client sử dụng voucher</t>
+  </si>
+  <si>
+    <t>Phải có ít nhất 1 voucher còn hạn và sử dụng được bởi khách mua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang đăng nhập (localhost:4200/login)
+3.	Xác nhận trang đăng nhập hiển thị thành công
+4.	Nhập thông tin đăng nhập
+5.	Xác nhận trang không báo lỗi
+6.	Bấm nút đăng nhập
+7.	Xác nhận trang bán hoa hiển thị thành công
+8.	Chọn sản phẩm bất kì
+9.	Chọn kích cỡ sản phẩm
+10.	Chọn màu sắc sản phẩm 
+11.	Nhấn nút "Thêm vào sản phẩm"
+12.	Nhấn vào icon giỏ hàng 
+13.	Xác nhận trang giỏ hàng hiển thị thành công 
+14.	Nhấn vào ô trống chọn sản phẩm cần thanh toán 
+15.	Nhấn nút "Tiến hành thanh toán"
+16.	Điền thông tin giao hàng 
+17.	Chọn phương thức thanh toán 
+18.	Chọn mã giảm giá
+19.	Nhấn nút "Thanh toán"
+20.	Truy cập trang admin (http://localhost:3000/)
+21.	Chọn mục "Thương hiệu"
+22.	Xác nhận số lượng của mã giảm giá đã thanh toán đã giảm</t>
+  </si>
+  <si>
+    <t>Thanh toán với voucher thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanh toán với voucher thành công </t>
+  </si>
+  <si>
+    <t>Xoá sản phẩm bên admin và client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+Phải có ít nhất 1 sản phẩm đang bán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+2.	Truy cập trang admin (localhost:3000)
+3.	Xác nhận trang admin hiển thị thành công
+4.	Chọn mục "Sản phẩm”
+5.	Bấm nút thùng rác của một sản phẩm trong danh sách
+6.	Xác nhận modal xác nhận xoá hiển thị
+7.	Bấm nút “Xoá sản phẩm”
+8.	Xác nhận sản phẩm có trạng thái đã xoá
+9.	Truy cập trang bán hoá (localhost:4200)
+10.	Xác nhận trang hiển thị
+11.	Xác nhận sản phẩm được xoá không có ở danh sách sản phẩm</t>
+  </si>
+  <si>
+    <t>Sản phẩm được xoá không có ở danh sách sản phẩm</t>
+  </si>
+  <si>
+    <t>AssertionError [ERR_ASSERTION]: 'Xóa mềm sản phẩm thất bại!' == 'Đã chuyển sản phẩm vào thùng rác!'</t>
+  </si>
+  <si>
+    <t>Xoá thương hiệu bên admin và client</t>
+  </si>
+  <si>
+    <t>AssertionError [ERR_ASSERTION]: 'Delete brand failed!' == 'Delete brand successfully!'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -975,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1007,11 +1098,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1025,47 +1146,23 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1399,760 +1496,351 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="22"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" ht="243" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
+    <row r="4" ht="384.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>156</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
+    <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
-    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="24.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="30" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="36.625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="47.875" customWidth="1"/>
+    <col min="5" max="5" width="29.125" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="8" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="19"/>
-    </row>
-    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" ht="314.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" ht="327.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11" t="s">
+    <row r="5" ht="171" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" ht="171" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>17</v>
+        <v>176</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" style="2" customWidth="1"/>
-    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-    </row>
-    <row r="3" spans="1:9" ht="285.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="242.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="270.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="256.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="10"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
@@ -2170,43 +1858,43 @@
     <col min="15" max="15" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="20" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
+    <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
@@ -2228,11 +1916,11 @@
       <c r="K2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" ht="357" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -2276,7 +1964,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -2320,7 +2008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2362,7 +2050,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
@@ -2404,7 +2092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>117</v>
       </c>
@@ -2417,7 +2105,7 @@
       <c r="D7" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -2448,7 +2136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>120</v>
       </c>
@@ -2461,7 +2149,7 @@
       <c r="D8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -2492,7 +2180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
@@ -2534,7 +2222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>126</v>
       </c>
@@ -2576,7 +2264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="285" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>128</v>
       </c>
@@ -2620,23 +2308,773 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17" style="2" customWidth="1"/>
+    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="185.25" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="10"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="100.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="114" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" ht="85.5" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" ht="99.75" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="9" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
+    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
+    <col min="7" max="7" width="24.875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="36.625" style="2" customWidth="1"/>
@@ -2648,53 +3086,53 @@
     <col min="10" max="10" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="23" t="s">
+      <c r="F1" s="20"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="13" t="s">
+    <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-    </row>
-    <row r="3" spans="1:10" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>133</v>
       </c>
@@ -2726,7 +3164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>139</v>
       </c>
@@ -2758,11 +3196,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="24" t="s">
         <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2787,11 +3225,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="24" t="s">
         <v>149</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2821,230 +3259,15 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" ht="243" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="384.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="356.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="17" customWidth="1"/>
-    <col min="3" max="8" width="17.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="17" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="17" t="s">
-        <v>166</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/selenium-tests/test-cases.xlsx
+++ b/selenium-tests/test-cases.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACB93DF-CB64-4B8E-9C77-7377BEFE2FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="6" name="Login" state="visible" r:id="rId4"/>
-    <sheet sheetId="7" name="Register" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="Cart" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="Checkout" state="visible" r:id="rId7"/>
-    <sheet sheetId="8" name="Filter" state="visible" r:id="rId8"/>
-    <sheet sheetId="10" name="Order" state="visible" r:id="rId9"/>
-    <sheet sheetId="12" name="IntegratedTests" state="visible" r:id="rId10"/>
+    <sheet name="Login" sheetId="6" r:id="rId1"/>
+    <sheet name="Register" sheetId="7" r:id="rId2"/>
+    <sheet name="Cart" sheetId="5" r:id="rId3"/>
+    <sheet name="Checkout" sheetId="3" r:id="rId4"/>
+    <sheet name="Filter" sheetId="8" r:id="rId5"/>
+    <sheet name="Order" sheetId="10" r:id="rId6"/>
+    <sheet name="IntegratedTests" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -61,7 +62,7 @@
     <t>Đã có tài khoản</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -88,7 +89,7 @@
     <t>Đăng nhập với email sai</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email không hợp lệ
@@ -107,7 +108,7 @@
     <t>Đăng nhập với email bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email bỏ trống
@@ -123,7 +124,7 @@
     <t>Đăng nhập với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu bỏ trống
@@ -139,7 +140,7 @@
     <t>Đăng nhập với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với email "nguyenquocthang909@gmail."
@@ -158,7 +159,7 @@
     <t>Đăng nhập với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập với mật khẩu "12345"
@@ -177,7 +178,7 @@
     <t>Đăng ký vói thông tin hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng ký (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký
@@ -197,7 +198,7 @@
     <t>Đăng ký với mật khẩu không khớp</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu không khớp
@@ -213,7 +214,7 @@
     <t>Đăng ký với email bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email bỏ trống
@@ -226,7 +227,7 @@
     <t>Đăng ký với mật khẩu bỏ trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu bỏ trống
@@ -239,7 +240,7 @@
     <t>Đăng ký với email định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với email "nguyenquocthang909@gmail."
@@ -252,7 +253,7 @@
     <t>Đăng ký với mật khẩu định dạng không hợp lệ</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký với mật khẩu và xác nhận mật khẩu "12345"
@@ -265,7 +266,7 @@
     <t>Đăng ký với thông tin đăng ký của một tài khoản đã có tồn tại trong CSDL</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng Nhập (localhost:4200/register)
 3.	Xác nhận trang đăng ký hiển thị thành công
 4.	Nhập thông tin đăng ký đã tồn tại
@@ -284,11 +285,11 @@
     <t>Thêm vào giỏ hàng thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Sản phẩm có tồn kho lớn hơn 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Bấm nút đăng nhập
@@ -312,11 +313,11 @@
     <t>Sản phẩm có trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -337,11 +338,11 @@
     <t>Tăng SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 0 trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang hiển thị thành công
 4.	Xác nhận trang bán hoa hiển thị thành công
@@ -367,11 +368,11 @@
     <t>Giảm SL sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm với số lượng lớn hơn 1 trong giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -396,7 +397,7 @@
     <t>Xoá sản phẩm từ giỏ hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm A
@@ -433,7 +434,7 @@
     <t>Thanh toán thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -481,12 +482,12 @@
     <t>Thanh toán với voucher hết hạn</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Có ít nhất 1 sản phẩm trong giỏ hàng
 Có ít nhất 1 voucher</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -519,7 +520,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập họ để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -545,7 +546,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập tên để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -571,7 +572,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập email để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -600,7 +601,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập SĐT để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -632,7 +633,7 @@
     <t>Thanh toán với thông tin thanh toán trường nhập ghi chú để trống</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Truy cập trang chi tiết sản phẩm ngẫu nhiên
@@ -664,7 +665,7 @@
     <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -685,7 +686,7 @@
     <t>Tìm kiếm sản phẩm với từ khoá không tồn tại trong các sản phẩm</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận thanh tìm kiếm hiển thị thành công
@@ -706,7 +707,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -725,7 +726,7 @@
     <t>Tìm kiếm và lọc sản phẩm theo giá với từ khoá</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Kéo thanh lọc giá đến giá trị định sẵn
@@ -741,7 +742,7 @@
     <t>Xem chi tiết đơn hàng được làm nổi bật</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -762,7 +763,7 @@
     <t>Huỷ đơn hàng</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -788,7 +789,7 @@
     <t>Huỷ đơn hàng không có lý do</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang bán hoa (localhost:4200)
 3.	Xác nhận trang bán hoa hiển thị thành công
 4.	Xác nhận hình cá nhân hiển thị thành công
@@ -813,7 +814,7 @@
     <t>Phải có ít nhất 1 sản phẩm đang bán</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -849,7 +850,7 @@
     <t>Phải có ít nhất 1 voucher còn hạn và sử dụng được bởi khách mua</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang đăng nhập (localhost:4200/login)
 3.	Xác nhận trang đăng nhập hiển thị thành công
 4.	Nhập thông tin đăng nhập
@@ -882,11 +883,11 @@
     <t>Xoá sản phẩm bên admin và client</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
+    <t>Đã có tài khoản và đang trong phiên đăng nhập với trang bán hoa
 Phải có ít nhất 1 sản phẩm đang bán</t>
   </si>
   <si>
-    <t xml:space="preserve">1.	Mở trình duyệt tùy chọn
+    <t>1.	Mở trình duyệt tùy chọn
 2.	Truy cập trang admin (localhost:3000)
 3.	Xác nhận trang admin hiển thị thành công
 4.	Chọn mục "Sản phẩm”
@@ -914,44 +915,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1107,33 +1108,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1146,11 +1120,38 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1158,11 +1159,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1496,405 +1497,814 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.8984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.8984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.69921875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.09765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="39.09765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.59765625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.8984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+    <row r="2" spans="1:9" ht="15" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" ht="243" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>151</v>
+      <c r="G2" s="19"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="100.5" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="384.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>155</v>
+    <row r="4" spans="1:9" ht="71.25" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="71.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="71.25" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="F6" s="8"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="356.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="25" t="s">
+    <row r="7" spans="1:9" ht="85.5" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="71.25" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="F8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="114" customHeight="1">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="85.5" customHeight="1">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="99.75" customHeight="1">
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="85.5" customHeight="1">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" ht="85.5" customHeight="1">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="99.75" customHeight="1">
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="99.75" customHeight="1">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" ht="85.5" customHeight="1">
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="36.625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="47.875" customWidth="1"/>
-    <col min="5" max="5" width="29.125" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="8" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="7.69921875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.8984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14" style="9" customWidth="1"/>
+    <col min="4" max="4" width="40.69921875" style="9" customWidth="1"/>
+    <col min="5" max="6" width="29.69921875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="24.8984375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="24.8984375" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="14" t="s">
+      <c r="F1" s="18"/>
+      <c r="G1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="17"/>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" ht="314.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>164</v>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="99.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="85.5" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="85.5" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="99.75" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" ht="327.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="99.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="85.5" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="171" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" s="7" t="s">
+    <row r="9" spans="1:9" ht="85.5" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" ht="171" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>99</v>
+      <c r="F9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="8.8984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.8984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17" style="2" customWidth="1"/>
+    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="21"/>
+      <c r="G1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+    </row>
+    <row r="3" spans="1:9" ht="285.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="242.25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="270.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="270.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="256.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="185.25" customHeight="1">
+      <c r="C8" s="10"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.19921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.69921875" style="1" customWidth="1"/>
     <col min="4" max="4" width="39" style="3" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.09765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" style="3" customWidth="1"/>
     <col min="7" max="7" width="11" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="3" customWidth="1"/>
-    <col min="12" max="13" width="24.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10.09765625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.3984375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="24.3984375" style="2" customWidth="1"/>
     <col min="14" max="14" width="6.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.875" customWidth="1"/>
+    <col min="15" max="15" width="17.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="5" t="s">
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+    <row r="2" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
@@ -1916,11 +2326,11 @@
       <c r="K2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" ht="357" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="18"/>
+    </row>
+    <row r="3" spans="1:14" ht="357" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -1964,7 +2374,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" ht="356.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="356.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -2008,7 +2418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="285" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2050,7 +2460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="285" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
@@ -2092,7 +2502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="285" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>117</v>
       </c>
@@ -2136,7 +2546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="285" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>120</v>
       </c>
@@ -2180,7 +2590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="285" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>122</v>
       </c>
@@ -2222,7 +2632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="285" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>126</v>
       </c>
@@ -2264,7 +2674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="285" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="285" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>128</v>
       </c>
@@ -2308,89 +2718,92 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" style="2" customWidth="1"/>
-    <col min="7" max="8" width="26.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
+    <col min="2" max="3" width="36.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.09765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.69921875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="33.09765625" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="14" t="s">
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="5" t="s">
+    <row r="2" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" ht="285.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+    </row>
+    <row r="3" spans="1:10" ht="129" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>69</v>
+        <v>134</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
@@ -2398,28 +2811,31 @@
       <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>68</v>
+      <c r="G3" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="242.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="114" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>73</v>
+        <v>140</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>14</v>
@@ -2428,27 +2844,30 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="128.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>77</v>
+        <v>144</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -2456,28 +2875,28 @@
       <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="270.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="128.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>82</v>
+        <v>148</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -2486,787 +2905,369 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" ht="256.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="185.25" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C8" s="10"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="35.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.19921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.3984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.8984375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="100.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="243" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="17" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
+    <row r="4" spans="1:9" ht="384.75" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>156</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
+    <row r="5" spans="1:9" ht="356.25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>160</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" ht="114" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" ht="85.5" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" ht="99.75" customHeight="1" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" ht="99.75" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" ht="85.5" customHeight="1" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" style="9" customWidth="1"/>
-    <col min="2" max="2" width="29.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="40.75" style="9" customWidth="1"/>
-    <col min="5" max="6" width="29.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="24.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="17.8984375" customWidth="1"/>
+    <col min="2" max="2" width="36.59765625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17.8984375" customWidth="1"/>
+    <col min="4" max="4" width="47.8984375" customWidth="1"/>
+    <col min="5" max="5" width="29.09765625" customWidth="1"/>
+    <col min="6" max="6" width="10.8984375" customWidth="1"/>
+    <col min="7" max="8" width="17.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
+    <row r="2" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+    </row>
+    <row r="3" spans="1:9" ht="314.25" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="327.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+    <row r="5" spans="1:9" ht="171" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="171" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="99.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" ht="85.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>17</v>
+        <v>176</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
-    <col min="2" max="3" width="36.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="45.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="33.125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-    </row>
-    <row r="3" ht="129" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="114" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="128.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
